--- a/experiments/04_lora_finetuning/report/leakage_honesty_check.xlsx
+++ b/experiments/04_lora_finetuning/report/leakage_honesty_check.xlsx
@@ -533,18 +533,18 @@
   <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/experiments/04_lora_finetuning/report/leakage_honesty_check.xlsx
+++ b/experiments/04_lora_finetuning/report/leakage_honesty_check.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,6 +26,12 @@
       <scheme val="minor"/>
     </font>
     <font/>
+    <font>
+      <color rgb="009C0006"/>
+    </font>
+    <font>
+      <color rgb="00006100"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -36,14 +42,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
-        <bgColor rgb="FF00B050"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -157,10 +163,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>

--- a/experiments/04_lora_finetuning/report/leakage_honesty_check.xlsx
+++ b/experiments/04_lora_finetuning/report/leakage_honesty_check.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,8 +32,11 @@
     <font>
       <color rgb="00006100"/>
     </font>
+    <font>
+      <color rgb="009C6500"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -52,6 +55,12 @@
         <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="9">
     <border>
@@ -156,7 +165,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -170,6 +179,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -696,7 +708,7 @@
       <c r="F4" s="5" t="n">
         <v>0.9297</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="7" t="n">
         <v>0.8421</v>
       </c>
       <c r="H4" s="4" t="n">
@@ -711,12 +723,12 @@
       <c r="K4" s="4" t="n">
         <v>0.9136</v>
       </c>
-      <c r="L4" s="5" t="n">
+      <c r="L4" s="7" t="n">
         <v>0.8471</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n"/>
+      <c r="A5" s="8" t="n"/>
       <c r="B5" s="1" t="inlineStr">
         <is>
           <t>enru</t>
@@ -770,13 +782,13 @@
       <c r="D6" s="5" t="n">
         <v>74.3</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="7" t="n">
         <v>60.12</v>
       </c>
       <c r="F6" s="4" t="n">
         <v>0.9088000000000001</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="G6" s="7" t="n">
         <v>0.8659</v>
       </c>
       <c r="H6" s="5" t="n">
@@ -785,13 +797,13 @@
       <c r="I6" s="4" t="n">
         <v>73.27</v>
       </c>
-      <c r="J6" s="5" t="n">
+      <c r="J6" s="7" t="n">
         <v>60.33</v>
       </c>
       <c r="K6" s="5" t="n">
         <v>0.9456</v>
       </c>
-      <c r="L6" s="5" t="n">
+      <c r="L6" s="7" t="n">
         <v>0.8743</v>
       </c>
     </row>
@@ -805,7 +817,7 @@
       <c r="C7" s="5" t="n">
         <v>57.71</v>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="7" t="n">
         <v>77.40000000000001</v>
       </c>
       <c r="E7" s="5" t="n">
@@ -814,13 +826,13 @@
       <c r="F7" s="5" t="n">
         <v>0.9346</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="7" t="n">
         <v>0.8538</v>
       </c>
       <c r="H7" s="4" t="n">
         <v>55.96</v>
       </c>
-      <c r="I7" s="4" t="n">
+      <c r="I7" s="7" t="n">
         <v>76.73</v>
       </c>
       <c r="J7" s="4" t="n">
@@ -829,12 +841,12 @@
       <c r="K7" s="4" t="n">
         <v>0.9227</v>
       </c>
-      <c r="L7" s="4" t="n">
+      <c r="L7" s="7" t="n">
         <v>0.8529</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="n"/>
+      <c r="A8" s="8" t="n"/>
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>enru</t>
@@ -894,7 +906,7 @@
       <c r="F9" s="4" t="n">
         <v>0.9099</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G9" s="7" t="n">
         <v>0.8715000000000001</v>
       </c>
       <c r="H9" s="4" t="n">
@@ -909,7 +921,7 @@
       <c r="K9" s="5" t="n">
         <v>0.9504</v>
       </c>
-      <c r="L9" s="5" t="n">
+      <c r="L9" s="7" t="n">
         <v>0.8743</v>
       </c>
     </row>
@@ -952,7 +964,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="n"/>
+      <c r="A11" s="8" t="n"/>
       <c r="B11" s="1" t="inlineStr">
         <is>
           <t>enru</t>
@@ -967,7 +979,7 @@
       <c r="E11" s="4" t="n">
         <v>65.58</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F11" s="7" t="n">
         <v>0.9031</v>
       </c>
       <c r="G11" s="4" t="n">
@@ -982,7 +994,7 @@
       <c r="J11" s="5" t="n">
         <v>70.11</v>
       </c>
-      <c r="K11" s="5" t="n">
+      <c r="K11" s="7" t="n">
         <v>0.9118000000000001</v>
       </c>
       <c r="L11" s="5" t="n">
